--- a/data/es/FittedTermStructure.xlsx
+++ b/data/es/FittedTermStructure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wme493\Documents\Sciebo\Projects\ICIE\inflation_app\data\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87CBD6F-3CC8-4E08-8A7B-0C0B016498C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{220E052A-F96A-4FFE-819C-7280E80C9F6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
